--- a/AR_overdue_zoho.xlsx
+++ b/AR_overdue_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O76"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 14/08/2026</t>
+As of 17/08/2026</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>310</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>270</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>254</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>223</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>223</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>223</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>189</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>176</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>103</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>510492000001403035</t>
+          <t>510492000001417001</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4912,17 +4912,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>242029</t>
+          <t>242032</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>510492000001025001</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>355.2</v>
+        <v>238.8</v>
       </c>
       <c r="N64" t="n">
-        <v>355.2</v>
+        <v>238.8</v>
       </c>
       <c r="O64" t="n">
         <v>1.0</v>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>510492000001417001</t>
+          <t>510492000001417033</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>242032</t>
+          <t>242034</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>510492000001417033</t>
+          <t>510492000001417049</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5050,17 +5050,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>242034</t>
+          <t>242035</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="N66" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O66" t="n">
         <v>1.0</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>510492000001417049</t>
+          <t>510492000001417066</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5119,17 +5119,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>242035</t>
+          <t>242036</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="N67" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="O67" t="n">
         <v>1.0</v>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>510492000001417066</t>
+          <t>510492000001417162</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>242036</t>
+          <t>242042</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000505059</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>Chorus Music Therapy &amp; Education</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="N68" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="O68" t="n">
         <v>1.0</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>510492000001417162</t>
+          <t>510492000001417242</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5257,17 +5257,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>242042</t>
+          <t>242047</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>510492000000505059</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Chorus Music Therapy &amp; Education</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="N69" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="O69" t="n">
         <v>1.0</v>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>510492000001417226</t>
+          <t>510492000001417338</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>242046</t>
+          <t>242053</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>510492000000742001</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Adam’s Painting and Decorating</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>510492000001417242</t>
+          <t>510492000001417386</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5395,17 +5395,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>242047</t>
+          <t>242056</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000001158053</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>PRIME GARDEN DESIGN LTD</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="N71" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="O71" t="n">
         <v>1.0</v>
@@ -5426,7 +5426,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>510492000001417338</t>
+          <t>510492000001429121</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5464,17 +5464,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>242053</t>
+          <t>242060</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000970001</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>Superhouse Education Foundation</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>240.0</v>
+        <v>1000.0</v>
       </c>
       <c r="N72" t="n">
-        <v>240.0</v>
+        <v>1000.0</v>
       </c>
       <c r="O72" t="n">
         <v>1.0</v>
@@ -5495,7 +5495,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>510492000001417386</t>
+          <t>510492000001445029</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5533,17 +5533,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>242056</t>
+          <t>242065</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>510492000001158053</t>
+          <t>510492000001445020</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>PRIME GARDEN DESIGN LTD</t>
+          <t>BORN FOR IT LTD</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5552,155 +5552,17 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>360.0</v>
+        <v>660.0</v>
       </c>
       <c r="N73" t="n">
-        <v>360.0</v>
+        <v>660.0</v>
       </c>
       <c r="O73" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>510492000001429121</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>242060</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>510492000000970001</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Superhouse Education Foundation</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M74" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="N74" t="n">
-        <v>1000.0</v>
-      </c>
-      <c r="O74" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>510492000001436115</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H75" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>242062</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>510492000001436106</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>RICHMOND TOTO PROFESSIONAL CLEANING LTD</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M75" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="N75" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="O75" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="55" t="inlineStr">
+      <c r="A74" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5709,7 +5571,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A76:O76"/>
+    <mergeCell ref="A74:O74"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_overdue_zoho.xlsx
+++ b/AR_overdue_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:O75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 17/08/2026</t>
+As of 20/08/2026</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>313</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>273</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>257</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>257</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>226</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>226</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>226</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>173</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>157</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>155</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4805,7 +4805,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>510492000001413033</t>
+          <t>510492000001417001</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4843,17 +4843,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>242031</t>
+          <t>242032</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>510492000001413024</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>88 DRIVING SCHOOL LTD</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>120.0</v>
+        <v>238.8</v>
       </c>
       <c r="N63" t="n">
-        <v>120.0</v>
+        <v>238.8</v>
       </c>
       <c r="O63" t="n">
         <v>1.0</v>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>510492000001417001</t>
+          <t>510492000001417033</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4912,17 +4912,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>242032</t>
+          <t>242034</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>510492000001417033</t>
+          <t>510492000001417049</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>242034</t>
+          <t>242035</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="N65" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O65" t="n">
         <v>1.0</v>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>510492000001417049</t>
+          <t>510492000001417066</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5050,17 +5050,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>242035</t>
+          <t>242036</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="N66" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="O66" t="n">
         <v>1.0</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>510492000001417066</t>
+          <t>510492000001417162</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5119,17 +5119,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>242036</t>
+          <t>242042</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000505059</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>Chorus Music Therapy &amp; Education</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="N67" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="O67" t="n">
         <v>1.0</v>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>510492000001417162</t>
+          <t>510492000001417242</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>242042</t>
+          <t>242047</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>510492000000505059</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Chorus Music Therapy &amp; Education</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="N68" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="O68" t="n">
         <v>1.0</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>510492000001417242</t>
+          <t>510492000001417338</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5257,17 +5257,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>242047</t>
+          <t>242053</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>510492000001417338</t>
+          <t>510492000001417386</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>242053</t>
+          <t>242056</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001158053</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>PRIME GARDEN DESIGN LTD</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="N70" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="O70" t="n">
         <v>1.0</v>
@@ -5357,7 +5357,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>510492000001417386</t>
+          <t>510492000001429121</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5395,17 +5395,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>242056</t>
+          <t>242060</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>510492000001158053</t>
+          <t>510492000000970001</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>PRIME GARDEN DESIGN LTD</t>
+          <t>Superhouse Education Foundation</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>360.0</v>
+        <v>1000.0</v>
       </c>
       <c r="N71" t="n">
-        <v>360.0</v>
+        <v>1000.0</v>
       </c>
       <c r="O71" t="n">
         <v>1.0</v>
@@ -5426,7 +5426,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>510492000001429121</t>
+          <t>510492000001445029</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5464,17 +5464,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>242060</t>
+          <t>242065</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>510492000000970001</t>
+          <t>510492000001445020</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Superhouse Education Foundation</t>
+          <t>BORN FOR IT LTD</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>1000.0</v>
+        <v>660.0</v>
       </c>
       <c r="N72" t="n">
-        <v>1000.0</v>
+        <v>660.0</v>
       </c>
       <c r="O72" t="n">
         <v>1.0</v>
@@ -5495,7 +5495,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>510492000001445029</t>
+          <t>510492000001450008</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5533,17 +5533,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>242065</t>
+          <t>242067</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>510492000001445020</t>
+          <t>510492000000327139</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>BORN FOR IT LTD</t>
+          <t>BATHROOMS LONDON LIMITED</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5552,17 +5552,86 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>660.0</v>
+        <v>400.0</v>
       </c>
       <c r="N73" t="n">
-        <v>660.0</v>
+        <v>400.0</v>
       </c>
       <c r="O73" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="55" t="inlineStr">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>overdue</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>510492000001450025</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>invoice</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>242068</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>510492000000122647</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>718.8</v>
+      </c>
+      <c r="N74" t="n">
+        <v>718.8</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5571,7 +5640,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A74:O74"/>
+    <mergeCell ref="A75:O75"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_overdue_zoho.xlsx
+++ b/AR_overdue_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 21/08/2026</t>
+As of 24/08/2026</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>317</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>277</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>261</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>261</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>230</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>230</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>230</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>183</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>183</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>171</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>171</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>171</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>159</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>510492000001180071</t>
+          <t>510492000001180143</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2428,17 +2428,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>241876</t>
+          <t>241878</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>510492000001180143</t>
+          <t>510492000001180178</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2493,21 +2493,21 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>241878</t>
+          <t>241879</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000240001</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>Cameraboss Photography</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>238.8</v>
+        <v>200.0</v>
       </c>
       <c r="N29" t="n">
-        <v>238.8</v>
+        <v>200.0</v>
       </c>
       <c r="O29" t="n">
         <v>1.0</v>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>510492000001180178</t>
+          <t>510492000001180423</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2566,17 +2566,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>241879</t>
+          <t>241886</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>510492000000240001</t>
+          <t>510492000000327139</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Cameraboss Photography</t>
+          <t>BATHROOMS LONDON LIMITED</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>200.0</v>
+        <v>360.0</v>
       </c>
       <c r="N30" t="n">
-        <v>200.0</v>
+        <v>360.0</v>
       </c>
       <c r="O30" t="n">
         <v>1.0</v>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>510492000001180423</t>
+          <t>510492000001180528</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2635,17 +2635,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>241886</t>
+          <t>241889</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>510492000000327139</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>BATHROOMS LONDON LIMITED</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>360.0</v>
+        <v>240.0</v>
       </c>
       <c r="N31" t="n">
-        <v>360.0</v>
+        <v>240.0</v>
       </c>
       <c r="O31" t="n">
         <v>1.0</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>510492000001180528</t>
+          <t>510492000001180633</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2704,17 +2704,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>241889</t>
+          <t>241892</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000000792001</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Edens Edge Limited</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2735,7 +2735,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>510492000001180633</t>
+          <t>510492000001231066</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2769,21 +2769,21 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>241892</t>
+          <t>241914</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>510492000000792001</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Edens Edge Limited</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="N33" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="O33" t="n">
         <v>1.0</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>510492000001231033</t>
+          <t>510492000001231082</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>241912</t>
+          <t>241915</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000240001</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Cameraboss Photography</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>238.8</v>
+        <v>200.0</v>
       </c>
       <c r="N34" t="n">
-        <v>238.8</v>
+        <v>200.0</v>
       </c>
       <c r="O34" t="n">
         <v>1.0</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>510492000001231066</t>
+          <t>510492000001231194</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2893,12 +2893,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2907,21 +2907,21 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>241914</t>
+          <t>241922</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000327139</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>BATHROOMS LONDON LIMITED</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2930,10 +2930,10 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>238.8</v>
+        <v>360.0</v>
       </c>
       <c r="N35" t="n">
-        <v>238.8</v>
+        <v>360.0</v>
       </c>
       <c r="O35" t="n">
         <v>1.0</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>510492000001231082</t>
+          <t>510492000001231242</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2980,17 +2980,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>241915</t>
+          <t>241925</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>510492000000240001</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Cameraboss Photography</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>200.0</v>
+        <v>240.0</v>
       </c>
       <c r="N36" t="n">
-        <v>200.0</v>
+        <v>240.0</v>
       </c>
       <c r="O36" t="n">
         <v>1.0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>510492000001231194</t>
+          <t>510492000001231370</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3031,12 +3031,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3049,17 +3049,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>241922</t>
+          <t>241933</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>510492000000327139</t>
+          <t>510492000001079001</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>BATHROOMS LONDON LIMITED</t>
+          <t>RBD Driving School</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>360.0</v>
+        <v>200.0</v>
       </c>
       <c r="N37" t="n">
-        <v>360.0</v>
+        <v>200.0</v>
       </c>
       <c r="O37" t="n">
         <v>1.0</v>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>510492000001231242</t>
+          <t>510492000001231386</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3118,17 +3118,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>241925</t>
+          <t>241934</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000001144276</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Creativa Ltd</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3149,7 +3149,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>510492000001231370</t>
+          <t>510492000001279033</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3183,21 +3183,21 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>241933</t>
+          <t>241949</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>510492000001079001</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>RBD Driving School</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3206,10 +3206,10 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>200.0</v>
+        <v>216.4</v>
       </c>
       <c r="N39" t="n">
-        <v>200.0</v>
+        <v>238.8</v>
       </c>
       <c r="O39" t="n">
         <v>1.0</v>
@@ -3218,7 +3218,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>510492000001231386</t>
+          <t>510492000001279049</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3252,21 +3252,21 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>241934</t>
+          <t>241950</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>510492000001144276</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Creativa Ltd</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>240.0</v>
+        <v>238.8</v>
       </c>
       <c r="N40" t="n">
-        <v>240.0</v>
+        <v>477.6</v>
       </c>
       <c r="O40" t="n">
         <v>1.0</v>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>510492000001279033</t>
+          <t>510492000001279066</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3325,17 +3325,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>241949</t>
+          <t>241951</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>510492000001279049</t>
+          <t>510492000001279242</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3390,21 +3390,21 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>241950</t>
+          <t>241962</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N42" t="n">
-        <v>477.6</v>
+        <v>240.0</v>
       </c>
       <c r="O42" t="n">
         <v>1.0</v>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>510492000001279066</t>
+          <t>510492000001279338</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3463,17 +3463,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>241951</t>
+          <t>241968</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N43" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O43" t="n">
         <v>1.0</v>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>510492000001279242</t>
+          <t>510492000001279370</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3532,17 +3532,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>241962</t>
+          <t>241970</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000001144276</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Creativa Ltd</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3563,7 +3563,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>510492000001279338</t>
+          <t>510492000001288131</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3583,12 +3583,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3597,21 +3597,21 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>241968</t>
+          <t>241975</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001111001</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>ABA CLEANING SERVICES LTD</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="N45" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="O45" t="n">
         <v>1.0</v>
@@ -3632,7 +3632,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>510492000001279370</t>
+          <t>510492000001300001</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3670,17 +3670,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>241970</t>
+          <t>241977</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>510492000001144276</t>
+          <t>510492000000387119</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Creativa Ltd</t>
+          <t>AUTO MARKET PLACE LIMITED</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>240.0</v>
+        <v>400.0</v>
       </c>
       <c r="N46" t="n">
-        <v>240.0</v>
+        <v>400.0</v>
       </c>
       <c r="O46" t="n">
         <v>1.0</v>
@@ -3701,7 +3701,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>510492000001288131</t>
+          <t>510492000001316001</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3739,17 +3739,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>241975</t>
+          <t>241979</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>510492000001111001</t>
+          <t>510492000001064041</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>ABA CLEANING SERVICES LTD</t>
+          <t>Jans Solutions Ltd</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>360.0</v>
+        <v>450.0</v>
       </c>
       <c r="N47" t="n">
-        <v>360.0</v>
+        <v>450.0</v>
       </c>
       <c r="O47" t="n">
         <v>1.0</v>
@@ -3770,7 +3770,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>510492000001300001</t>
+          <t>510492000001338001</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3790,12 +3790,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3808,17 +3808,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>241977</t>
+          <t>241984</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>510492000000387119</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>AUTO MARKET PLACE LIMITED</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>400.0</v>
+        <v>238.8</v>
       </c>
       <c r="N48" t="n">
-        <v>400.0</v>
+        <v>238.8</v>
       </c>
       <c r="O48" t="n">
         <v>1.0</v>
@@ -3839,7 +3839,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>510492000001316001</t>
+          <t>510492000001338033</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3877,17 +3877,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>241979</t>
+          <t>241986</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>510492000001064041</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Jans Solutions Ltd</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>450.0</v>
+        <v>238.8</v>
       </c>
       <c r="N49" t="n">
-        <v>450.0</v>
+        <v>238.8</v>
       </c>
       <c r="O49" t="n">
         <v>1.0</v>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>510492000001338001</t>
+          <t>510492000001338049</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3946,17 +3946,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>241984</t>
+          <t>241987</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="N50" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O50" t="n">
         <v>1.0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>510492000001338033</t>
+          <t>510492000001338066</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4015,17 +4015,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>241986</t>
+          <t>241988</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>510492000001338049</t>
+          <t>510492000001338242</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4084,17 +4084,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>241987</t>
+          <t>241999</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>477.6</v>
+        <v>240.0</v>
       </c>
       <c r="N52" t="n">
-        <v>477.6</v>
+        <v>240.0</v>
       </c>
       <c r="O52" t="n">
         <v>1.0</v>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>510492000001338066</t>
+          <t>510492000001338338</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4153,17 +4153,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>241988</t>
+          <t>242005</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N53" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O53" t="n">
         <v>1.0</v>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>510492000001338242</t>
+          <t>510492000001338370</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4222,17 +4222,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>241999</t>
+          <t>242007</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000001144276</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Creativa Ltd</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4253,7 +4253,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>510492000001338338</t>
+          <t>510492000001359025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>242005</t>
+          <t>242012</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000317525</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>EAGLE PROPERTY CARE</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>240.0</v>
+        <v>250.0</v>
       </c>
       <c r="N55" t="n">
-        <v>240.0</v>
+        <v>250.0</v>
       </c>
       <c r="O55" t="n">
         <v>1.0</v>
@@ -4322,7 +4322,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>510492000001338370</t>
+          <t>510492000001359061</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4360,17 +4360,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>242007</t>
+          <t>242014</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>510492000001144276</t>
+          <t>510492000001088061</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Creativa Ltd</t>
+          <t>Drive with Greta</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>240.0</v>
+        <v>150.0</v>
       </c>
       <c r="N56" t="n">
-        <v>240.0</v>
+        <v>150.0</v>
       </c>
       <c r="O56" t="n">
         <v>1.0</v>
@@ -4391,7 +4391,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>510492000001359025</t>
+          <t>510492000001367083</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4429,17 +4429,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>242012</t>
+          <t>242015</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>510492000000317525</t>
+          <t>510492000000946037</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>EAGLE PROPERTY CARE</t>
+          <t>Ace Learning Plus Limited</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4448,10 +4448,10 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>250.0</v>
+        <v>450.0</v>
       </c>
       <c r="N57" t="n">
-        <v>250.0</v>
+        <v>450.0</v>
       </c>
       <c r="O57" t="n">
         <v>1.0</v>
@@ -4460,7 +4460,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>510492000001359061</t>
+          <t>510492000001388001</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>242014</t>
+          <t>242021</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>150.0</v>
+        <v>360.0</v>
       </c>
       <c r="N58" t="n">
-        <v>150.0</v>
+        <v>360.0</v>
       </c>
       <c r="O58" t="n">
         <v>1.0</v>
@@ -4529,7 +4529,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>510492000001367083</t>
+          <t>510492000001391088</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4567,17 +4567,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>242015</t>
+          <t>242026</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>510492000000946037</t>
+          <t>510492000001391079</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Ace Learning Plus Limited</t>
+          <t>NGS Plumbing &amp; Heating Ltd</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>450.0</v>
+        <v>75.0</v>
       </c>
       <c r="N59" t="n">
-        <v>450.0</v>
+        <v>75.0</v>
       </c>
       <c r="O59" t="n">
         <v>1.0</v>
@@ -4598,7 +4598,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>510492000001388001</t>
+          <t>510492000001403010</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>242021</t>
+          <t>242027</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>510492000001088061</t>
+          <t>510492000001403001</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Drive with Greta</t>
+          <t>Malvern Renovation</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>360.0</v>
+        <v>120.0</v>
       </c>
       <c r="N60" t="n">
-        <v>360.0</v>
+        <v>120.0</v>
       </c>
       <c r="O60" t="n">
         <v>1.0</v>
@@ -4667,7 +4667,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>510492000001391088</t>
+          <t>510492000001417001</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4705,17 +4705,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>242026</t>
+          <t>242032</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>510492000001391079</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>NGS Plumbing &amp; Heating Ltd</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>75.0</v>
+        <v>238.8</v>
       </c>
       <c r="N61" t="n">
-        <v>75.0</v>
+        <v>238.8</v>
       </c>
       <c r="O61" t="n">
         <v>1.0</v>
@@ -4736,7 +4736,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>510492000001403010</t>
+          <t>510492000001417033</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4774,17 +4774,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>242027</t>
+          <t>242034</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>510492000001403001</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Malvern Renovation</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>120.0</v>
+        <v>238.8</v>
       </c>
       <c r="N62" t="n">
-        <v>120.0</v>
+        <v>238.8</v>
       </c>
       <c r="O62" t="n">
         <v>1.0</v>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>510492000001417001</t>
+          <t>510492000001417049</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4843,17 +4843,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>242032</t>
+          <t>242035</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="N63" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O63" t="n">
         <v>1.0</v>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>510492000001417033</t>
+          <t>510492000001417066</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4912,17 +4912,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>242034</t>
+          <t>242036</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>510492000001417049</t>
+          <t>510492000001417162</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>242035</t>
+          <t>242042</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000505059</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>Chorus Music Therapy &amp; Education</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>477.6</v>
+        <v>120.0</v>
       </c>
       <c r="N65" t="n">
-        <v>477.6</v>
+        <v>120.0</v>
       </c>
       <c r="O65" t="n">
         <v>1.0</v>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>510492000001417066</t>
+          <t>510492000001417242</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5050,17 +5050,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>242036</t>
+          <t>242047</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N66" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O66" t="n">
         <v>1.0</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>510492000001417162</t>
+          <t>510492000001417338</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5119,17 +5119,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>242042</t>
+          <t>242053</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>510492000000505059</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Chorus Music Therapy &amp; Education</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="N67" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="O67" t="n">
         <v>1.0</v>
@@ -5150,7 +5150,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>510492000001417242</t>
+          <t>510492000001429121</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>242047</t>
+          <t>242060</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000000970001</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Superhouse Education Foundation</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>240.0</v>
+        <v>1000.0</v>
       </c>
       <c r="N68" t="n">
-        <v>240.0</v>
+        <v>1000.0</v>
       </c>
       <c r="O68" t="n">
         <v>1.0</v>
@@ -5219,7 +5219,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>510492000001417338</t>
+          <t>510492000001445029</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5257,17 +5257,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>242053</t>
+          <t>242065</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001445020</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>BORN FOR IT LTD</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>240.0</v>
+        <v>660.0</v>
       </c>
       <c r="N69" t="n">
-        <v>240.0</v>
+        <v>660.0</v>
       </c>
       <c r="O69" t="n">
         <v>1.0</v>
@@ -5288,7 +5288,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>510492000001417386</t>
+          <t>510492000001450008</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>242056</t>
+          <t>242067</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>510492000001158053</t>
+          <t>510492000000327139</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>PRIME GARDEN DESIGN LTD</t>
+          <t>BATHROOMS LONDON LIMITED</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>360.0</v>
+        <v>400.0</v>
       </c>
       <c r="N70" t="n">
-        <v>360.0</v>
+        <v>400.0</v>
       </c>
       <c r="O70" t="n">
         <v>1.0</v>
@@ -5357,7 +5357,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>510492000001429121</t>
+          <t>510492000001450025</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5391,21 +5391,21 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>242060</t>
+          <t>242068</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>510492000000970001</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Superhouse Education Foundation</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5414,224 +5414,17 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>1000.0</v>
+        <v>718.8</v>
       </c>
       <c r="N71" t="n">
-        <v>1000.0</v>
+        <v>718.8</v>
       </c>
       <c r="O71" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>510492000001445029</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H72" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>242065</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>510492000001445020</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>BORN FOR IT LTD</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M72" t="n">
-        <v>660.0</v>
-      </c>
-      <c r="N72" t="n">
-        <v>660.0</v>
-      </c>
-      <c r="O72" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>510492000001450008</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>242067</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>510492000000327139</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>BATHROOMS LONDON LIMITED</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M73" t="n">
-        <v>400.0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>400.0</v>
-      </c>
-      <c r="O73" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>510492000001450025</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>242068</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>510492000000122647</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M74" t="n">
-        <v>718.8</v>
-      </c>
-      <c r="N74" t="n">
-        <v>718.8</v>
-      </c>
-      <c r="O74" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="55" t="inlineStr">
+      <c r="A72" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5640,7 +5433,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A75:O75"/>
+    <mergeCell ref="A72:O72"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/AR_overdue_zoho.xlsx
+++ b/AR_overdue_zoho.xlsx
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 24/08/2026</t>
+As of 27/08/2026</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>320</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>280</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>264</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>264</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>233</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>233</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>233</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>186</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>113</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>510492000001279049</t>
+          <t>510492000001279066</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3256,17 +3256,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>241950</t>
+          <t>241951</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3278,7 +3278,7 @@
         <v>238.8</v>
       </c>
       <c r="N40" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="O40" t="n">
         <v>1.0</v>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>510492000001279066</t>
+          <t>510492000001279242</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>241951</t>
+          <t>241962</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N41" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O41" t="n">
         <v>1.0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>510492000001279242</t>
+          <t>510492000001279370</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3394,17 +3394,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>241962</t>
+          <t>241970</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000001144276</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Creativa Ltd</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3425,7 +3425,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>510492000001279338</t>
+          <t>510492000001288131</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3445,12 +3445,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>81</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3459,21 +3459,21 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>241968</t>
+          <t>241975</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000001111001</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>ABA CLEANING SERVICES LTD</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="N43" t="n">
-        <v>240.0</v>
+        <v>360.0</v>
       </c>
       <c r="O43" t="n">
         <v>1.0</v>
@@ -3494,7 +3494,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>510492000001279370</t>
+          <t>510492000001300001</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3532,17 +3532,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>241970</t>
+          <t>241977</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>510492000001144276</t>
+          <t>510492000000387119</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Creativa Ltd</t>
+          <t>AUTO MARKET PLACE LIMITED</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>240.0</v>
+        <v>400.0</v>
       </c>
       <c r="N44" t="n">
-        <v>240.0</v>
+        <v>400.0</v>
       </c>
       <c r="O44" t="n">
         <v>1.0</v>
@@ -3563,7 +3563,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>510492000001288131</t>
+          <t>510492000001316001</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3583,12 +3583,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>241975</t>
+          <t>241979</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>510492000001111001</t>
+          <t>510492000001064041</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>ABA CLEANING SERVICES LTD</t>
+          <t>Jans Solutions Ltd</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>360.0</v>
+        <v>450.0</v>
       </c>
       <c r="N45" t="n">
-        <v>360.0</v>
+        <v>450.0</v>
       </c>
       <c r="O45" t="n">
         <v>1.0</v>
@@ -3632,7 +3632,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>510492000001300001</t>
+          <t>510492000001338001</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3670,17 +3670,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>241977</t>
+          <t>241984</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>510492000000387119</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>AUTO MARKET PLACE LIMITED</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>400.0</v>
+        <v>238.8</v>
       </c>
       <c r="N46" t="n">
-        <v>400.0</v>
+        <v>238.8</v>
       </c>
       <c r="O46" t="n">
         <v>1.0</v>
@@ -3701,7 +3701,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>510492000001316001</t>
+          <t>510492000001338033</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3739,17 +3739,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>241979</t>
+          <t>241986</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>510492000001064041</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Jans Solutions Ltd</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>450.0</v>
+        <v>238.8</v>
       </c>
       <c r="N47" t="n">
-        <v>450.0</v>
+        <v>238.8</v>
       </c>
       <c r="O47" t="n">
         <v>1.0</v>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>510492000001338001</t>
+          <t>510492000001338049</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3808,17 +3808,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>241984</t>
+          <t>241987</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3830,7 +3830,7 @@
         <v>238.8</v>
       </c>
       <c r="N48" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O48" t="n">
         <v>1.0</v>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>510492000001338033</t>
+          <t>510492000001338066</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3877,17 +3877,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>241986</t>
+          <t>241988</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>510492000001338049</t>
+          <t>510492000001338242</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3946,17 +3946,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>241987</t>
+          <t>241999</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>477.6</v>
+        <v>240.0</v>
       </c>
       <c r="N50" t="n">
-        <v>477.6</v>
+        <v>240.0</v>
       </c>
       <c r="O50" t="n">
         <v>1.0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>510492000001338066</t>
+          <t>510492000001338338</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4015,17 +4015,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>241988</t>
+          <t>242005</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4034,10 +4034,10 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N51" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O51" t="n">
         <v>1.0</v>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>510492000001338242</t>
+          <t>510492000001338370</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>52</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4084,17 +4084,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>241999</t>
+          <t>242007</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000001144276</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Creativa Ltd</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4115,7 +4115,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>510492000001338338</t>
+          <t>510492000001359025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4153,17 +4153,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>242005</t>
+          <t>242012</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000317525</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>EAGLE PROPERTY CARE</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>240.0</v>
+        <v>250.0</v>
       </c>
       <c r="N53" t="n">
-        <v>240.0</v>
+        <v>250.0</v>
       </c>
       <c r="O53" t="n">
         <v>1.0</v>
@@ -4184,7 +4184,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>510492000001338370</t>
+          <t>510492000001367083</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4222,17 +4222,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>242007</t>
+          <t>242015</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>510492000001144276</t>
+          <t>510492000000946037</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Creativa Ltd</t>
+          <t>Ace Learning Plus Limited</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>240.0</v>
+        <v>450.0</v>
       </c>
       <c r="N54" t="n">
-        <v>240.0</v>
+        <v>450.0</v>
       </c>
       <c r="O54" t="n">
         <v>1.0</v>
@@ -4253,7 +4253,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>510492000001359025</t>
+          <t>510492000001388001</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>242012</t>
+          <t>242021</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>510492000000317525</t>
+          <t>510492000001088061</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>EAGLE PROPERTY CARE</t>
+          <t>Drive with Greta</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>250.0</v>
+        <v>360.0</v>
       </c>
       <c r="N55" t="n">
-        <v>250.0</v>
+        <v>360.0</v>
       </c>
       <c r="O55" t="n">
         <v>1.0</v>
@@ -4322,7 +4322,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>510492000001359061</t>
+          <t>510492000001391088</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4360,17 +4360,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>242014</t>
+          <t>242026</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>510492000001088061</t>
+          <t>510492000001391079</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Drive with Greta</t>
+          <t>NGS Plumbing &amp; Heating Ltd</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>150.0</v>
+        <v>75.0</v>
       </c>
       <c r="N56" t="n">
-        <v>150.0</v>
+        <v>75.0</v>
       </c>
       <c r="O56" t="n">
         <v>1.0</v>
@@ -4391,7 +4391,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>510492000001367083</t>
+          <t>510492000001403010</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4429,17 +4429,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>242015</t>
+          <t>242027</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>510492000000946037</t>
+          <t>510492000001403001</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Ace Learning Plus Limited</t>
+          <t>Malvern Renovation</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4448,10 +4448,10 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>450.0</v>
+        <v>120.0</v>
       </c>
       <c r="N57" t="n">
-        <v>450.0</v>
+        <v>120.0</v>
       </c>
       <c r="O57" t="n">
         <v>1.0</v>
@@ -4460,7 +4460,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>510492000001388001</t>
+          <t>510492000001417001</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4498,17 +4498,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>242021</t>
+          <t>242032</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>510492000001088061</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Drive with Greta</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>360.0</v>
+        <v>238.8</v>
       </c>
       <c r="N58" t="n">
-        <v>360.0</v>
+        <v>238.8</v>
       </c>
       <c r="O58" t="n">
         <v>1.0</v>
@@ -4529,7 +4529,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>510492000001391088</t>
+          <t>510492000001417033</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4567,17 +4567,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>242026</t>
+          <t>242034</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>510492000001391079</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>NGS Plumbing &amp; Heating Ltd</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>75.0</v>
+        <v>238.8</v>
       </c>
       <c r="N59" t="n">
-        <v>75.0</v>
+        <v>238.8</v>
       </c>
       <c r="O59" t="n">
         <v>1.0</v>
@@ -4598,7 +4598,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>510492000001403010</t>
+          <t>510492000001417049</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>242027</t>
+          <t>242035</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>510492000001403001</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Malvern Renovation</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>120.0</v>
+        <v>477.6</v>
       </c>
       <c r="N60" t="n">
-        <v>120.0</v>
+        <v>477.6</v>
       </c>
       <c r="O60" t="n">
         <v>1.0</v>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>510492000001417001</t>
+          <t>510492000001417066</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4705,17 +4705,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>242032</t>
+          <t>242036</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>510492000001417033</t>
+          <t>510492000001417162</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4774,17 +4774,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>242034</t>
+          <t>242042</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000505059</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Chorus Music Therapy &amp; Education</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="N62" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="O62" t="n">
         <v>1.0</v>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>510492000001417049</t>
+          <t>510492000001417242</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4843,17 +4843,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>242035</t>
+          <t>242047</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4862,10 +4862,10 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>477.6</v>
+        <v>240.0</v>
       </c>
       <c r="N63" t="n">
-        <v>477.6</v>
+        <v>240.0</v>
       </c>
       <c r="O63" t="n">
         <v>1.0</v>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>510492000001417066</t>
+          <t>510492000001417338</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4912,17 +4912,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>242036</t>
+          <t>242053</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="N64" t="n">
-        <v>238.8</v>
+        <v>240.0</v>
       </c>
       <c r="O64" t="n">
         <v>1.0</v>
@@ -4943,7 +4943,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>510492000001417162</t>
+          <t>510492000001429121</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>242042</t>
+          <t>242060</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>510492000000505059</t>
+          <t>510492000000970001</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Chorus Music Therapy &amp; Education</t>
+          <t>Superhouse Education Foundation</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>120.0</v>
+        <v>1000.0</v>
       </c>
       <c r="N65" t="n">
-        <v>120.0</v>
+        <v>1000.0</v>
       </c>
       <c r="O65" t="n">
         <v>1.0</v>
@@ -5012,7 +5012,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>510492000001417242</t>
+          <t>510492000001445029</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5050,17 +5050,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>242047</t>
+          <t>242065</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000001445020</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>BORN FOR IT LTD</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>240.0</v>
+        <v>660.0</v>
       </c>
       <c r="N66" t="n">
-        <v>240.0</v>
+        <v>660.0</v>
       </c>
       <c r="O66" t="n">
         <v>1.0</v>
@@ -5081,7 +5081,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>510492000001417338</t>
+          <t>510492000001450008</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5119,17 +5119,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>242053</t>
+          <t>242067</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000327139</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>BATHROOMS LONDON LIMITED</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>240.0</v>
+        <v>400.0</v>
       </c>
       <c r="N67" t="n">
-        <v>240.0</v>
+        <v>400.0</v>
       </c>
       <c r="O67" t="n">
         <v>1.0</v>
@@ -5150,7 +5150,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>510492000001429121</t>
+          <t>510492000001450025</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5184,21 +5184,21 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>242060</t>
+          <t>242068</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>510492000000970001</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Superhouse Education Foundation</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>1000.0</v>
+        <v>718.8</v>
       </c>
       <c r="N68" t="n">
-        <v>1000.0</v>
+        <v>718.8</v>
       </c>
       <c r="O68" t="n">
         <v>1.0</v>
@@ -5219,7 +5219,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>510492000001445029</t>
+          <t>510492000001460089</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5257,17 +5257,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>242065</t>
+          <t>242075</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>510492000001445020</t>
+          <t>510492000000639001</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>BORN FOR IT LTD</t>
+          <t>De'Osa Engineering Services</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>660.0</v>
+        <v>120.0</v>
       </c>
       <c r="N69" t="n">
-        <v>660.0</v>
+        <v>120.0</v>
       </c>
       <c r="O69" t="n">
         <v>1.0</v>
@@ -5288,7 +5288,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>510492000001450008</t>
+          <t>510492000001460115</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>242067</t>
+          <t>242076</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>510492000000327139</t>
+          <t>510492000001460106</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>BATHROOMS LONDON LIMITED</t>
+          <t>MOUNTAINS OF GLORY</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>400.0</v>
+        <v>250.0</v>
       </c>
       <c r="N70" t="n">
-        <v>400.0</v>
+        <v>250.0</v>
       </c>
       <c r="O70" t="n">
         <v>1.0</v>
@@ -5357,7 +5357,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>510492000001450025</t>
+          <t>510492000001460138</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5391,21 +5391,21 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>242068</t>
+          <t>242077</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000386033</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>ALPHA EUROPE LTD</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5414,10 +5414,10 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>718.8</v>
+        <v>240.0</v>
       </c>
       <c r="N71" t="n">
-        <v>718.8</v>
+        <v>240.0</v>
       </c>
       <c r="O71" t="n">
         <v>1.0</v>

--- a/AR_overdue_zoho.xlsx
+++ b/AR_overdue_zoho.xlsx
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O72"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.0625" customWidth="true"/>
@@ -581,7 +581,7 @@
         <is>
           <t>Sparta Telecom Ltd T/A Fast Ranking
 AR Aging Details
-As of 27/08/2026</t>
+As of 01/09/2026</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>325</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>285</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>269</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>269</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>238</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>238</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>238</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>207</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>207</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>207</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>204</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>204</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>191</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>191</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>185</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>179</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>169</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>167</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>86</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4115,7 +4115,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>510492000001359025</t>
+          <t>510492000001367083</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4153,17 +4153,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>242012</t>
+          <t>242015</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>510492000000317525</t>
+          <t>510492000000946037</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>EAGLE PROPERTY CARE</t>
+          <t>Ace Learning Plus Limited</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>250.0</v>
+        <v>450.0</v>
       </c>
       <c r="N53" t="n">
-        <v>250.0</v>
+        <v>450.0</v>
       </c>
       <c r="O53" t="n">
         <v>1.0</v>
@@ -4184,7 +4184,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>510492000001367083</t>
+          <t>510492000001388001</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4222,17 +4222,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>242015</t>
+          <t>242021</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>510492000000946037</t>
+          <t>510492000001088061</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Ace Learning Plus Limited</t>
+          <t>Drive with Greta</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>450.0</v>
+        <v>360.0</v>
       </c>
       <c r="N54" t="n">
-        <v>450.0</v>
+        <v>360.0</v>
       </c>
       <c r="O54" t="n">
         <v>1.0</v>
@@ -4253,7 +4253,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>510492000001388001</t>
+          <t>510492000001391088</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>242021</t>
+          <t>242026</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>510492000001088061</t>
+          <t>510492000001391079</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Drive with Greta</t>
+          <t>NGS Plumbing &amp; Heating Ltd</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4310,10 +4310,10 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>360.0</v>
+        <v>75.0</v>
       </c>
       <c r="N55" t="n">
-        <v>360.0</v>
+        <v>75.0</v>
       </c>
       <c r="O55" t="n">
         <v>1.0</v>
@@ -4322,7 +4322,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>510492000001391088</t>
+          <t>510492000001403010</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4360,17 +4360,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>242026</t>
+          <t>242027</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>510492000001391079</t>
+          <t>510492000001403001</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>NGS Plumbing &amp; Heating Ltd</t>
+          <t>Malvern Renovation</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4379,10 +4379,10 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>75.0</v>
+        <v>120.0</v>
       </c>
       <c r="N56" t="n">
-        <v>75.0</v>
+        <v>120.0</v>
       </c>
       <c r="O56" t="n">
         <v>1.0</v>
@@ -4391,7 +4391,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>510492000001403010</t>
+          <t>510492000001417001</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4429,17 +4429,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>242027</t>
+          <t>242032</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>510492000001403001</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Malvern Renovation</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4448,10 +4448,10 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>120.0</v>
+        <v>238.8</v>
       </c>
       <c r="N57" t="n">
-        <v>120.0</v>
+        <v>238.8</v>
       </c>
       <c r="O57" t="n">
         <v>1.0</v>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>510492000001417001</t>
+          <t>510492000001417033</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4498,17 +4498,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>242032</t>
+          <t>242034</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000123247</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>NOMADS CLOTHING LIMITED</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>510492000001417033</t>
+          <t>510492000001417049</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4567,17 +4567,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>242034</t>
+          <t>242035</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>510492000000123247</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>NOMADS CLOTHING LIMITED</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="N59" t="n">
-        <v>238.8</v>
+        <v>477.6</v>
       </c>
       <c r="O59" t="n">
         <v>1.0</v>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>510492000001417049</t>
+          <t>510492000001417066</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>242035</t>
+          <t>242036</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000192073</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>SUPERHOUSE (UK) LIMITED</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="N60" t="n">
-        <v>477.6</v>
+        <v>238.8</v>
       </c>
       <c r="O60" t="n">
         <v>1.0</v>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>510492000001417066</t>
+          <t>510492000001417162</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4705,17 +4705,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>242036</t>
+          <t>242042</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>510492000000192073</t>
+          <t>510492000000505059</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>SUPERHOUSE (UK) LIMITED</t>
+          <t>Chorus Music Therapy &amp; Education</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4724,10 +4724,10 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="N61" t="n">
-        <v>238.8</v>
+        <v>120.0</v>
       </c>
       <c r="O61" t="n">
         <v>1.0</v>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>510492000001417162</t>
+          <t>510492000001417242</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4774,17 +4774,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>242042</t>
+          <t>242047</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>510492000000505059</t>
+          <t>510492000000560319</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Chorus Music Therapy &amp; Education</t>
+          <t>RRJ Carpentry and Joinery Ltd</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="N62" t="n">
-        <v>120.0</v>
+        <v>240.0</v>
       </c>
       <c r="O62" t="n">
         <v>1.0</v>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>510492000001417242</t>
+          <t>510492000001417338</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4843,17 +4843,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>242047</t>
+          <t>242053</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>510492000000560319</t>
+          <t>510492000000123277</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>RRJ Carpentry and Joinery Ltd</t>
+          <t>Patrick Shoes Limited</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4874,7 +4874,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>510492000001417338</t>
+          <t>510492000001429121</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4912,17 +4912,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>242053</t>
+          <t>242060</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>510492000000123277</t>
+          <t>510492000000970001</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Patrick Shoes Limited</t>
+          <t>Superhouse Education Foundation</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>240.0</v>
+        <v>1000.0</v>
       </c>
       <c r="N64" t="n">
-        <v>240.0</v>
+        <v>1000.0</v>
       </c>
       <c r="O64" t="n">
         <v>1.0</v>
@@ -4943,7 +4943,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>510492000001429121</t>
+          <t>510492000001445029</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>242060</t>
+          <t>242065</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>510492000000970001</t>
+          <t>510492000001445020</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Superhouse Education Foundation</t>
+          <t>BORN FOR IT LTD</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5000,10 +5000,10 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>1000.0</v>
+        <v>660.0</v>
       </c>
       <c r="N65" t="n">
-        <v>1000.0</v>
+        <v>660.0</v>
       </c>
       <c r="O65" t="n">
         <v>1.0</v>
@@ -5012,7 +5012,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>510492000001445029</t>
+          <t>510492000001450008</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5050,17 +5050,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>242065</t>
+          <t>242067</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>510492000001445020</t>
+          <t>510492000000327139</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>BORN FOR IT LTD</t>
+          <t>BATHROOMS LONDON LIMITED</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>660.0</v>
+        <v>400.0</v>
       </c>
       <c r="N66" t="n">
-        <v>660.0</v>
+        <v>400.0</v>
       </c>
       <c r="O66" t="n">
         <v>1.0</v>
@@ -5081,7 +5081,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>510492000001450008</t>
+          <t>510492000001450025</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5115,21 +5115,21 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>242067</t>
+          <t>242068</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>510492000000327139</t>
+          <t>510492000000122647</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>BATHROOMS LONDON LIMITED</t>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>400.0</v>
+        <v>718.8</v>
       </c>
       <c r="N67" t="n">
-        <v>400.0</v>
+        <v>718.8</v>
       </c>
       <c r="O67" t="n">
         <v>1.0</v>
@@ -5150,7 +5150,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>510492000001450025</t>
+          <t>510492000001460089</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5184,21 +5184,21 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>242068</t>
+          <t>242075</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>510492000000122647</t>
+          <t>510492000000639001</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+          <t>De'Osa Engineering Services</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>718.8</v>
+        <v>120.0</v>
       </c>
       <c r="N68" t="n">
-        <v>718.8</v>
+        <v>120.0</v>
       </c>
       <c r="O68" t="n">
         <v>1.0</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>510492000001460089</t>
+          <t>510492000001460115</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5257,17 +5257,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>242075</t>
+          <t>242076</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>510492000000639001</t>
+          <t>510492000001460106</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>De'Osa Engineering Services</t>
+          <t>MOUNTAINS OF GLORY</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>120.0</v>
+        <v>250.0</v>
       </c>
       <c r="N69" t="n">
-        <v>120.0</v>
+        <v>250.0</v>
       </c>
       <c r="O69" t="n">
         <v>1.0</v>
@@ -5288,7 +5288,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>510492000001460115</t>
+          <t>510492000001460138</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>242076</t>
+          <t>242077</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>510492000001460106</t>
+          <t>510492000000386033</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>MOUNTAINS OF GLORY</t>
+          <t>ALPHA EUROPE LTD</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5345,86 +5345,17 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>250.0</v>
+        <v>240.0</v>
       </c>
       <c r="N70" t="n">
-        <v>250.0</v>
+        <v>240.0</v>
       </c>
       <c r="O70" t="n">
         <v>1.0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>overdue</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>510492000001460138</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>invoice</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>242077</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>510492000000386033</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>ALPHA EUROPE LTD</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="M71" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>240.0</v>
-      </c>
-      <c r="O71" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="55" t="inlineStr">
+      <c r="A71" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -5433,7 +5364,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A72:O72"/>
+    <mergeCell ref="A71:O71"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
